--- a/backend/config/nickname_song.xlsx
+++ b/backend/config/nickname_song.xlsx
@@ -1,21 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MyKoishiCode\tsugu-bot\external\tsugu-bangdream-bot\backend\config\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\dev\tsugu-bangdream-bot\backend\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C15634C5-1237-4AF2-9480-46C3B4626A4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F537F9E-17D7-48D1-82F1-3B3E27C0E3AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2232" yWindow="768" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="23452" windowHeight="12682" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">工作表1!$A$1:$C$605</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1906,9 +1914,6 @@
     <t>EXIST</t>
   </si>
   <si>
-    <t>存在,exi,扰乱op,ex,大e3,我有e育症</t>
-  </si>
-  <si>
     <t>Live Beyond!!</t>
   </si>
   <si>
@@ -3581,6 +3586,10 @@
   </si>
   <si>
     <t>希腊奶,各位群友晚上好,lzn,六兆年</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>存在,exi,扰乱op,ex,大e3,e,我有e育症</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -3965,8 +3974,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:C605"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.796875" customWidth="1"/>
     <col min="2" max="2" width="50.796875" customWidth="1"/>
@@ -3974,7 +3984,7 @@
     <col min="4" max="4" width="55.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3985,7 +3995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -3996,7 +4006,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -4007,7 +4017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
@@ -4018,7 +4028,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
@@ -4029,7 +4039,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
@@ -4040,7 +4050,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>7</v>
       </c>
@@ -4051,7 +4061,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>8</v>
       </c>
@@ -4062,7 +4072,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>9</v>
       </c>
@@ -4073,7 +4083,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>10</v>
       </c>
@@ -4084,7 +4094,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>11</v>
       </c>
@@ -4095,7 +4105,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>12</v>
       </c>
@@ -4106,7 +4116,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>13</v>
       </c>
@@ -4117,7 +4127,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>14</v>
       </c>
@@ -4128,7 +4138,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>15</v>
       </c>
@@ -4139,7 +4149,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>16</v>
       </c>
@@ -4150,7 +4160,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>17</v>
       </c>
@@ -4161,7 +4171,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>18</v>
       </c>
@@ -4172,7 +4182,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>19</v>
       </c>
@@ -4183,7 +4193,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>20</v>
       </c>
@@ -4194,7 +4204,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>21</v>
       </c>
@@ -4205,7 +4215,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>22</v>
       </c>
@@ -4216,7 +4226,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>24</v>
       </c>
@@ -4227,7 +4237,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>25</v>
       </c>
@@ -4238,7 +4248,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>26</v>
       </c>
@@ -4249,7 +4259,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>27</v>
       </c>
@@ -4260,7 +4270,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>28</v>
       </c>
@@ -4271,7 +4281,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>29</v>
       </c>
@@ -4282,7 +4292,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>30</v>
       </c>
@@ -4293,7 +4303,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>31</v>
       </c>
@@ -4304,7 +4314,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>32</v>
       </c>
@@ -4315,7 +4325,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>33</v>
       </c>
@@ -4326,7 +4336,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>34</v>
       </c>
@@ -4337,7 +4347,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>35</v>
       </c>
@@ -4348,7 +4358,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>36</v>
       </c>
@@ -4359,7 +4369,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>37</v>
       </c>
@@ -4370,7 +4380,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37">
         <v>40</v>
       </c>
@@ -4381,7 +4391,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>41</v>
       </c>
@@ -4392,7 +4402,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>42</v>
       </c>
@@ -4403,7 +4413,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="40" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>43</v>
       </c>
@@ -4414,7 +4424,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>44</v>
       </c>
@@ -4425,7 +4435,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>45</v>
       </c>
@@ -4436,7 +4446,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="43" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>46</v>
       </c>
@@ -4447,7 +4457,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>47</v>
       </c>
@@ -4458,7 +4468,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>48</v>
       </c>
@@ -4469,7 +4479,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="46" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>49</v>
       </c>
@@ -4480,7 +4490,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>50</v>
       </c>
@@ -4491,7 +4501,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>51</v>
       </c>
@@ -4502,7 +4512,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="49" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>52</v>
       </c>
@@ -4513,7 +4523,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="50" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>53</v>
       </c>
@@ -4524,7 +4534,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>54</v>
       </c>
@@ -4535,7 +4545,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>55</v>
       </c>
@@ -4546,7 +4556,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>56</v>
       </c>
@@ -4557,7 +4567,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>57</v>
       </c>
@@ -4568,7 +4578,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55">
         <v>58</v>
       </c>
@@ -4579,7 +4589,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>59</v>
       </c>
@@ -4590,7 +4600,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>60</v>
       </c>
@@ -4601,7 +4611,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>61</v>
       </c>
@@ -4612,7 +4622,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>62</v>
       </c>
@@ -4623,7 +4633,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>63</v>
       </c>
@@ -4634,7 +4644,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>64</v>
       </c>
@@ -4645,7 +4655,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>65</v>
       </c>
@@ -4656,7 +4666,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>66</v>
       </c>
@@ -4667,7 +4677,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>67</v>
       </c>
@@ -4678,7 +4688,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="65" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>68</v>
       </c>
@@ -4689,7 +4699,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="66" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>69</v>
       </c>
@@ -4700,7 +4710,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="67" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>70</v>
       </c>
@@ -4711,7 +4721,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="68" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>71</v>
       </c>
@@ -4722,7 +4732,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="69" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>72</v>
       </c>
@@ -4733,7 +4743,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="70" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>73</v>
       </c>
@@ -4744,7 +4754,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="71" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71">
         <v>74</v>
       </c>
@@ -4755,7 +4765,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>75</v>
       </c>
@@ -4766,7 +4776,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="73" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>76</v>
       </c>
@@ -4777,7 +4787,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="74" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>77</v>
       </c>
@@ -4788,7 +4798,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="75" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>78</v>
       </c>
@@ -4799,7 +4809,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="76" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>79</v>
       </c>
@@ -4810,7 +4820,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="77" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>80</v>
       </c>
@@ -4821,7 +4831,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="78" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>81</v>
       </c>
@@ -4832,7 +4842,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="79" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>82</v>
       </c>
@@ -4843,7 +4853,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="80" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>83</v>
       </c>
@@ -4854,7 +4864,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="81" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>84</v>
       </c>
@@ -4865,7 +4875,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="82" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>85</v>
       </c>
@@ -4876,7 +4886,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="83" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>86</v>
       </c>
@@ -4887,7 +4897,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="84" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>87</v>
       </c>
@@ -4898,7 +4908,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="85" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>88</v>
       </c>
@@ -4909,7 +4919,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="86" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86">
         <v>89</v>
       </c>
@@ -4920,7 +4930,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="87" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87">
         <v>90</v>
       </c>
@@ -4931,7 +4941,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="88" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88">
         <v>91</v>
       </c>
@@ -4942,7 +4952,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="89" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89">
         <v>92</v>
       </c>
@@ -4953,7 +4963,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="90" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90">
         <v>93</v>
       </c>
@@ -4964,7 +4974,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="91" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91">
         <v>94</v>
       </c>
@@ -4975,7 +4985,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92">
         <v>95</v>
       </c>
@@ -4986,7 +4996,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="93" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93">
         <v>96</v>
       </c>
@@ -4997,7 +5007,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="94" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94">
         <v>97</v>
       </c>
@@ -5008,7 +5018,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="95" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95">
         <v>100</v>
       </c>
@@ -5019,7 +5029,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="96" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96">
         <v>101</v>
       </c>
@@ -5030,7 +5040,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="97" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97">
         <v>104</v>
       </c>
@@ -5041,7 +5051,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="98" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98">
         <v>105</v>
       </c>
@@ -5052,7 +5062,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="99" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99">
         <v>106</v>
       </c>
@@ -5063,7 +5073,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="100" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100">
         <v>107</v>
       </c>
@@ -5074,7 +5084,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101">
         <v>108</v>
       </c>
@@ -5085,7 +5095,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="102" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102">
         <v>109</v>
       </c>
@@ -5096,7 +5106,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="103" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103">
         <v>110</v>
       </c>
@@ -5107,7 +5117,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104">
         <v>111</v>
       </c>
@@ -5118,7 +5128,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105">
         <v>112</v>
       </c>
@@ -5129,7 +5139,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="106" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106">
         <v>113</v>
       </c>
@@ -5140,7 +5150,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="107" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107">
         <v>115</v>
       </c>
@@ -5151,7 +5161,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="108" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108">
         <v>116</v>
       </c>
@@ -5162,7 +5172,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="109" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109">
         <v>117</v>
       </c>
@@ -5173,7 +5183,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="110" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110">
         <v>118</v>
       </c>
@@ -5184,7 +5194,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="111" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111">
         <v>119</v>
       </c>
@@ -5195,7 +5205,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="112" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112">
         <v>120</v>
       </c>
@@ -5206,7 +5216,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="113" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113">
         <v>121</v>
       </c>
@@ -5217,7 +5227,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="114" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114">
         <v>122</v>
       </c>
@@ -5228,7 +5238,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="115" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115">
         <v>123</v>
       </c>
@@ -5239,7 +5249,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="116" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116">
         <v>124</v>
       </c>
@@ -5250,7 +5260,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="117" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117">
         <v>125</v>
       </c>
@@ -5261,7 +5271,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="118" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A118">
         <v>126</v>
       </c>
@@ -5272,7 +5282,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="119" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119">
         <v>127</v>
       </c>
@@ -5283,7 +5293,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="120" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120">
         <v>128</v>
       </c>
@@ -5291,10 +5301,10 @@
         <v>239</v>
       </c>
       <c r="C120" t="s">
-        <v>1186</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121">
         <v>129</v>
       </c>
@@ -5305,7 +5315,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="122" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122">
         <v>130</v>
       </c>
@@ -5316,7 +5326,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="123" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123">
         <v>131</v>
       </c>
@@ -5327,7 +5337,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="124" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124">
         <v>132</v>
       </c>
@@ -5338,7 +5348,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="125" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125">
         <v>133</v>
       </c>
@@ -5349,7 +5359,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="126" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126">
         <v>134</v>
       </c>
@@ -5360,7 +5370,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="127" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127">
         <v>135</v>
       </c>
@@ -5371,7 +5381,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="128" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128">
         <v>136</v>
       </c>
@@ -5382,7 +5392,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="129" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129">
         <v>137</v>
       </c>
@@ -5393,7 +5403,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="130" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130">
         <v>138</v>
       </c>
@@ -5404,7 +5414,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="131" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131">
         <v>139</v>
       </c>
@@ -5415,7 +5425,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="132" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132">
         <v>140</v>
       </c>
@@ -5426,7 +5436,7 @@
         <v>263</v>
       </c>
     </row>
-    <row r="133" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133">
         <v>141</v>
       </c>
@@ -5437,7 +5447,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="134" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134">
         <v>142</v>
       </c>
@@ -5448,7 +5458,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="135" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135">
         <v>143</v>
       </c>
@@ -5459,7 +5469,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="136" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136">
         <v>144</v>
       </c>
@@ -5470,7 +5480,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="137" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137">
         <v>145</v>
       </c>
@@ -5481,7 +5491,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="138" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138">
         <v>146</v>
       </c>
@@ -5492,7 +5502,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="139" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139">
         <v>147</v>
       </c>
@@ -5503,7 +5513,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="140" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140">
         <v>148</v>
       </c>
@@ -5514,7 +5524,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="141" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141">
         <v>149</v>
       </c>
@@ -5525,7 +5535,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="142" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142">
         <v>150</v>
       </c>
@@ -5536,7 +5546,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="143" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143">
         <v>151</v>
       </c>
@@ -5547,7 +5557,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="144" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144">
         <v>152</v>
       </c>
@@ -5558,7 +5568,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="145" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145">
         <v>153</v>
       </c>
@@ -5569,7 +5579,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="146" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146">
         <v>154</v>
       </c>
@@ -5580,7 +5590,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="147" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147">
         <v>155</v>
       </c>
@@ -5591,7 +5601,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="148" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148">
         <v>156</v>
       </c>
@@ -5602,7 +5612,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="149" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149">
         <v>157</v>
       </c>
@@ -5613,7 +5623,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="150" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150">
         <v>158</v>
       </c>
@@ -5624,7 +5634,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="151" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151">
         <v>159</v>
       </c>
@@ -5635,7 +5645,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="152" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152">
         <v>160</v>
       </c>
@@ -5646,7 +5656,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="153" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153">
         <v>161</v>
       </c>
@@ -5657,7 +5667,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="154" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154">
         <v>162</v>
       </c>
@@ -5668,7 +5678,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="155" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155">
         <v>163</v>
       </c>
@@ -5679,7 +5689,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="156" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156">
         <v>164</v>
       </c>
@@ -5690,7 +5700,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="157" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157">
         <v>165</v>
       </c>
@@ -5701,7 +5711,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="158" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158">
         <v>166</v>
       </c>
@@ -5712,7 +5722,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="159" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159">
         <v>167</v>
       </c>
@@ -5723,7 +5733,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="160" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160">
         <v>168</v>
       </c>
@@ -5734,7 +5744,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="161" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161">
         <v>169</v>
       </c>
@@ -5745,7 +5755,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="162" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162">
         <v>170</v>
       </c>
@@ -5756,7 +5766,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="163" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163">
         <v>171</v>
       </c>
@@ -5767,7 +5777,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="164" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164">
         <v>172</v>
       </c>
@@ -5778,7 +5788,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="165" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165">
         <v>173</v>
       </c>
@@ -5789,7 +5799,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="166" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166">
         <v>174</v>
       </c>
@@ -5800,7 +5810,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="167" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167">
         <v>175</v>
       </c>
@@ -5811,7 +5821,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="168" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168">
         <v>176</v>
       </c>
@@ -5822,7 +5832,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="169" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169">
         <v>177</v>
       </c>
@@ -5833,7 +5843,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="170" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170">
         <v>178</v>
       </c>
@@ -5844,7 +5854,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="171" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171">
         <v>179</v>
       </c>
@@ -5855,7 +5865,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="172" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172">
         <v>180</v>
       </c>
@@ -5866,7 +5876,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="173" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173">
         <v>181</v>
       </c>
@@ -5877,7 +5887,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="174" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174">
         <v>182</v>
       </c>
@@ -5888,7 +5898,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="175" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175">
         <v>183</v>
       </c>
@@ -5899,7 +5909,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="176" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176">
         <v>184</v>
       </c>
@@ -5910,7 +5920,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="177" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177">
         <v>185</v>
       </c>
@@ -5921,7 +5931,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="178" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178">
         <v>186</v>
       </c>
@@ -5932,7 +5942,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="179" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179">
         <v>187</v>
       </c>
@@ -5943,7 +5953,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="180" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180">
         <v>188</v>
       </c>
@@ -5954,7 +5964,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="181" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181">
         <v>189</v>
       </c>
@@ -5965,7 +5975,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="182" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182">
         <v>190</v>
       </c>
@@ -5976,7 +5986,7 @@
         <v>363</v>
       </c>
     </row>
-    <row r="183" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183">
         <v>191</v>
       </c>
@@ -5987,7 +5997,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="184" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184">
         <v>192</v>
       </c>
@@ -5998,7 +6008,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="185" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185">
         <v>193</v>
       </c>
@@ -6009,7 +6019,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="186" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186">
         <v>194</v>
       </c>
@@ -6020,7 +6030,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="187" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187">
         <v>195</v>
       </c>
@@ -6031,7 +6041,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="188" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188">
         <v>196</v>
       </c>
@@ -6042,7 +6052,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="189" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189">
         <v>197</v>
       </c>
@@ -6053,7 +6063,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="190" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190">
         <v>198</v>
       </c>
@@ -6064,7 +6074,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="191" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191">
         <v>199</v>
       </c>
@@ -6075,7 +6085,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="192" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192">
         <v>200</v>
       </c>
@@ -6086,7 +6096,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="193" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193">
         <v>201</v>
       </c>
@@ -6097,7 +6107,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="194" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194">
         <v>202</v>
       </c>
@@ -6108,7 +6118,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="195" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195">
         <v>203</v>
       </c>
@@ -6119,7 +6129,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="196" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196">
         <v>204</v>
       </c>
@@ -6130,7 +6140,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="197" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197">
         <v>205</v>
       </c>
@@ -6141,7 +6151,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="198" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198">
         <v>206</v>
       </c>
@@ -6152,7 +6162,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="199" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199">
         <v>207</v>
       </c>
@@ -6163,7 +6173,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="200" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200">
         <v>208</v>
       </c>
@@ -6174,7 +6184,7 @@
         <v>399</v>
       </c>
     </row>
-    <row r="201" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201">
         <v>209</v>
       </c>
@@ -6185,7 +6195,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="202" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202">
         <v>210</v>
       </c>
@@ -6196,7 +6206,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="203" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203">
         <v>211</v>
       </c>
@@ -6207,7 +6217,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="204" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204">
         <v>212</v>
       </c>
@@ -6218,7 +6228,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="205" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205">
         <v>213</v>
       </c>
@@ -6229,7 +6239,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="206" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206">
         <v>214</v>
       </c>
@@ -6240,7 +6250,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="207" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207">
         <v>215</v>
       </c>
@@ -6251,7 +6261,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="208" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208">
         <v>217</v>
       </c>
@@ -6262,7 +6272,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="209" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209">
         <v>218</v>
       </c>
@@ -6273,7 +6283,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="210" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210">
         <v>219</v>
       </c>
@@ -6284,7 +6294,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="211" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211">
         <v>220</v>
       </c>
@@ -6295,7 +6305,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="212" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212">
         <v>221</v>
       </c>
@@ -6306,7 +6316,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="213" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213">
         <v>222</v>
       </c>
@@ -6317,7 +6327,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="214" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214">
         <v>223</v>
       </c>
@@ -6328,7 +6338,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="215" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215">
         <v>224</v>
       </c>
@@ -6339,7 +6349,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="216" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216">
         <v>225</v>
       </c>
@@ -6350,7 +6360,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="217" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217">
         <v>226</v>
       </c>
@@ -6361,7 +6371,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="218" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218">
         <v>227</v>
       </c>
@@ -6372,7 +6382,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="219" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219">
         <v>228</v>
       </c>
@@ -6383,7 +6393,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="220" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220">
         <v>229</v>
       </c>
@@ -6394,7 +6404,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="221" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221">
         <v>230</v>
       </c>
@@ -6405,7 +6415,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="222" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222">
         <v>231</v>
       </c>
@@ -6416,7 +6426,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="223" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223">
         <v>232</v>
       </c>
@@ -6427,7 +6437,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="224" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224">
         <v>233</v>
       </c>
@@ -6438,7 +6448,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="225" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225">
         <v>234</v>
       </c>
@@ -6449,7 +6459,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="226" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226">
         <v>235</v>
       </c>
@@ -6460,7 +6470,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="227" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227">
         <v>236</v>
       </c>
@@ -6471,7 +6481,7 @@
         <v>453</v>
       </c>
     </row>
-    <row r="228" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228">
         <v>237</v>
       </c>
@@ -6482,7 +6492,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="229" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229">
         <v>238</v>
       </c>
@@ -6493,7 +6503,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="230" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230">
         <v>239</v>
       </c>
@@ -6504,7 +6514,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="231" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231">
         <v>240</v>
       </c>
@@ -6515,7 +6525,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="232" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232">
         <v>241</v>
       </c>
@@ -6526,7 +6536,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="233" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233">
         <v>242</v>
       </c>
@@ -6537,7 +6547,7 @@
         <v>465</v>
       </c>
     </row>
-    <row r="234" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234">
         <v>243</v>
       </c>
@@ -6548,7 +6558,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="235" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235">
         <v>244</v>
       </c>
@@ -6559,7 +6569,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="236" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236">
         <v>245</v>
       </c>
@@ -6570,7 +6580,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="237" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237">
         <v>246</v>
       </c>
@@ -6581,7 +6591,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="238" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238">
         <v>247</v>
       </c>
@@ -6592,7 +6602,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="239" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239">
         <v>248</v>
       </c>
@@ -6603,7 +6613,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="240" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240">
         <v>249</v>
       </c>
@@ -6614,7 +6624,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="241" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241">
         <v>250</v>
       </c>
@@ -6625,7 +6635,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="242" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242">
         <v>251</v>
       </c>
@@ -6636,7 +6646,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="243" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243">
         <v>252</v>
       </c>
@@ -6647,7 +6657,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="244" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244">
         <v>253</v>
       </c>
@@ -6658,7 +6668,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="245" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245">
         <v>254</v>
       </c>
@@ -6669,7 +6679,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="246" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246">
         <v>255</v>
       </c>
@@ -6680,7 +6690,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="247" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247">
         <v>256</v>
       </c>
@@ -6691,7 +6701,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="248" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248">
         <v>257</v>
       </c>
@@ -6702,7 +6712,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="249" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249">
         <v>258</v>
       </c>
@@ -6713,7 +6723,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="250" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250">
         <v>259</v>
       </c>
@@ -6724,7 +6734,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="251" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251">
         <v>260</v>
       </c>
@@ -6735,7 +6745,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="252" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A252">
         <v>261</v>
       </c>
@@ -6746,7 +6756,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="253" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253">
         <v>262</v>
       </c>
@@ -6757,7 +6767,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="254" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254">
         <v>263</v>
       </c>
@@ -6768,7 +6778,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="255" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255">
         <v>264</v>
       </c>
@@ -6779,7 +6789,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="256" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256">
         <v>265</v>
       </c>
@@ -6790,7 +6800,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="257" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A257">
         <v>266</v>
       </c>
@@ -6801,7 +6811,7 @@
         <v>512</v>
       </c>
     </row>
-    <row r="258" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258">
         <v>267</v>
       </c>
@@ -6812,7 +6822,7 @@
         <v>514</v>
       </c>
     </row>
-    <row r="259" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A259">
         <v>268</v>
       </c>
@@ -6823,7 +6833,7 @@
         <v>516</v>
       </c>
     </row>
-    <row r="260" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260">
         <v>269</v>
       </c>
@@ -6834,7 +6844,7 @@
         <v>518</v>
       </c>
     </row>
-    <row r="261" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261">
         <v>270</v>
       </c>
@@ -6845,7 +6855,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="262" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A262">
         <v>271</v>
       </c>
@@ -6856,7 +6866,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="263" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263">
         <v>272</v>
       </c>
@@ -6867,7 +6877,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="264" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264">
         <v>274</v>
       </c>
@@ -6878,7 +6888,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="265" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265">
         <v>275</v>
       </c>
@@ -6889,7 +6899,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="266" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266">
         <v>276</v>
       </c>
@@ -6900,7 +6910,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="267" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267">
         <v>277</v>
       </c>
@@ -6911,7 +6921,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="268" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268">
         <v>278</v>
       </c>
@@ -6922,7 +6932,7 @@
         <v>534</v>
       </c>
     </row>
-    <row r="269" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269">
         <v>279</v>
       </c>
@@ -6933,7 +6943,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="270" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270">
         <v>280</v>
       </c>
@@ -6944,7 +6954,7 @@
         <v>538</v>
       </c>
     </row>
-    <row r="271" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271">
         <v>281</v>
       </c>
@@ -6955,7 +6965,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="272" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272">
         <v>282</v>
       </c>
@@ -6966,7 +6976,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="273" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273">
         <v>283</v>
       </c>
@@ -6977,7 +6987,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="274" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A274">
         <v>284</v>
       </c>
@@ -6988,7 +6998,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="275" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275">
         <v>285</v>
       </c>
@@ -6999,7 +7009,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="276" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A276">
         <v>286</v>
       </c>
@@ -7010,7 +7020,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="277" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277">
         <v>287</v>
       </c>
@@ -7021,7 +7031,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="278" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278">
         <v>288</v>
       </c>
@@ -7032,7 +7042,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="279" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279">
         <v>289</v>
       </c>
@@ -7043,7 +7053,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="280" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280">
         <v>290</v>
       </c>
@@ -7054,7 +7064,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="281" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A281">
         <v>291</v>
       </c>
@@ -7065,7 +7075,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="282" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282">
         <v>292</v>
       </c>
@@ -7076,7 +7086,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="283" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283">
         <v>293</v>
       </c>
@@ -7087,7 +7097,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="284" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284">
         <v>294</v>
       </c>
@@ -7098,7 +7108,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="285" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285">
         <v>295</v>
       </c>
@@ -7109,7 +7119,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="286" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286">
         <v>296</v>
       </c>
@@ -7120,7 +7130,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="287" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A287">
         <v>297</v>
       </c>
@@ -7131,7 +7141,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="288" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288">
         <v>298</v>
       </c>
@@ -7142,7 +7152,7 @@
         <v>574</v>
       </c>
     </row>
-    <row r="289" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289">
         <v>299</v>
       </c>
@@ -7153,7 +7163,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="290" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290">
         <v>300</v>
       </c>
@@ -7164,7 +7174,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="291" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A291">
         <v>301</v>
       </c>
@@ -7175,7 +7185,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="292" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292">
         <v>302</v>
       </c>
@@ -7186,7 +7196,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="293" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A293">
         <v>303</v>
       </c>
@@ -7197,7 +7207,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="294" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294">
         <v>304</v>
       </c>
@@ -7208,7 +7218,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="295" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295">
         <v>305</v>
       </c>
@@ -7219,7 +7229,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="296" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296">
         <v>306</v>
       </c>
@@ -7230,7 +7240,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="297" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A297">
         <v>307</v>
       </c>
@@ -7241,7 +7251,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="298" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298">
         <v>308</v>
       </c>
@@ -7252,7 +7262,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="299" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A299">
         <v>309</v>
       </c>
@@ -7263,7 +7273,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="300" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300">
         <v>310</v>
       </c>
@@ -7274,7 +7284,7 @@
         <v>598</v>
       </c>
     </row>
-    <row r="301" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301">
         <v>311</v>
       </c>
@@ -7285,7 +7295,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="302" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302">
         <v>312</v>
       </c>
@@ -7296,7 +7306,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="303" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303">
         <v>313</v>
       </c>
@@ -7307,7 +7317,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="304" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304">
         <v>314</v>
       </c>
@@ -7318,7 +7328,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="305" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A305">
         <v>315</v>
       </c>
@@ -7329,7 +7339,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="306" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A306">
         <v>316</v>
       </c>
@@ -7340,7 +7350,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="307" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307">
         <v>317</v>
       </c>
@@ -7351,7 +7361,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="308" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308">
         <v>318</v>
       </c>
@@ -7362,7 +7372,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="309" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309">
         <v>319</v>
       </c>
@@ -7373,7 +7383,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="310" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310">
         <v>320</v>
       </c>
@@ -7384,7 +7394,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="311" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311">
         <v>321</v>
       </c>
@@ -7395,7 +7405,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="312" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312">
         <v>322</v>
       </c>
@@ -7406,7 +7416,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="313" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A313">
         <v>323</v>
       </c>
@@ -7417,7 +7427,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="314" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314">
         <v>324</v>
       </c>
@@ -7428,7 +7438,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="315" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A315">
         <v>325</v>
       </c>
@@ -7436,3159 +7446,3168 @@
         <v>627</v>
       </c>
       <c r="C315" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="316" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A316">
         <v>326</v>
       </c>
       <c r="B316" t="s">
+        <v>628</v>
+      </c>
+      <c r="C316" t="s">
         <v>629</v>
       </c>
-      <c r="C316" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="317" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317">
         <v>327</v>
       </c>
       <c r="B317" t="s">
+        <v>630</v>
+      </c>
+      <c r="C317" t="s">
         <v>631</v>
       </c>
-      <c r="C317" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="318" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A318">
         <v>328</v>
       </c>
       <c r="B318" t="s">
+        <v>632</v>
+      </c>
+      <c r="C318" t="s">
         <v>633</v>
       </c>
-      <c r="C318" t="s">
-        <v>634</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="319" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319">
         <v>329</v>
       </c>
       <c r="B319" t="s">
+        <v>634</v>
+      </c>
+      <c r="C319" t="s">
         <v>635</v>
       </c>
-      <c r="C319" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="320" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A320">
         <v>330</v>
       </c>
       <c r="B320" t="s">
+        <v>636</v>
+      </c>
+      <c r="C320" t="s">
         <v>637</v>
       </c>
-      <c r="C320" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="321" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="321" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A321">
         <v>331</v>
       </c>
       <c r="B321" t="s">
+        <v>638</v>
+      </c>
+      <c r="C321" t="s">
         <v>639</v>
       </c>
-      <c r="C321" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="322" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="322" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A322">
         <v>332</v>
       </c>
       <c r="B322" t="s">
+        <v>640</v>
+      </c>
+      <c r="C322" t="s">
         <v>641</v>
       </c>
-      <c r="C322" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="323" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="323" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A323">
         <v>333</v>
       </c>
       <c r="B323" t="s">
+        <v>642</v>
+      </c>
+      <c r="C323" t="s">
         <v>643</v>
       </c>
-      <c r="C323" t="s">
-        <v>644</v>
-      </c>
-    </row>
-    <row r="324" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="324" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324">
         <v>334</v>
       </c>
       <c r="B324" t="s">
+        <v>644</v>
+      </c>
+      <c r="C324" t="s">
         <v>645</v>
       </c>
-      <c r="C324" t="s">
-        <v>646</v>
-      </c>
-    </row>
-    <row r="325" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="325" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A325">
         <v>335</v>
       </c>
       <c r="B325" t="s">
+        <v>646</v>
+      </c>
+      <c r="C325" t="s">
         <v>647</v>
       </c>
-      <c r="C325" t="s">
-        <v>648</v>
-      </c>
-    </row>
-    <row r="326" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="326" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A326">
         <v>336</v>
       </c>
       <c r="B326" t="s">
+        <v>648</v>
+      </c>
+      <c r="C326" t="s">
         <v>649</v>
       </c>
-      <c r="C326" t="s">
-        <v>650</v>
-      </c>
-    </row>
-    <row r="327" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="327" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A327">
         <v>337</v>
       </c>
       <c r="B327" t="s">
+        <v>650</v>
+      </c>
+      <c r="C327" t="s">
         <v>651</v>
       </c>
-      <c r="C327" t="s">
-        <v>652</v>
-      </c>
-    </row>
-    <row r="328" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="328" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A328">
         <v>338</v>
       </c>
       <c r="B328" t="s">
+        <v>652</v>
+      </c>
+      <c r="C328" t="s">
         <v>653</v>
       </c>
-      <c r="C328" t="s">
-        <v>654</v>
-      </c>
-    </row>
-    <row r="329" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="329" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A329">
         <v>339</v>
       </c>
       <c r="B329" t="s">
+        <v>654</v>
+      </c>
+      <c r="C329" t="s">
         <v>655</v>
       </c>
-      <c r="C329" t="s">
-        <v>656</v>
-      </c>
-    </row>
-    <row r="330" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="330" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A330">
         <v>340</v>
       </c>
       <c r="B330" t="s">
+        <v>656</v>
+      </c>
+      <c r="C330" t="s">
         <v>657</v>
       </c>
-      <c r="C330" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="331" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="331" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A331">
         <v>341</v>
       </c>
       <c r="B331" t="s">
+        <v>658</v>
+      </c>
+      <c r="C331" t="s">
         <v>659</v>
       </c>
-      <c r="C331" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="332" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="332" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A332">
         <v>342</v>
       </c>
       <c r="B332" t="s">
+        <v>660</v>
+      </c>
+      <c r="C332" t="s">
         <v>661</v>
       </c>
-      <c r="C332" t="s">
-        <v>662</v>
-      </c>
-    </row>
-    <row r="333" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A333">
         <v>343</v>
       </c>
       <c r="B333" t="s">
+        <v>662</v>
+      </c>
+      <c r="C333" t="s">
         <v>663</v>
       </c>
-      <c r="C333" t="s">
-        <v>664</v>
-      </c>
-    </row>
-    <row r="334" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="334" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A334">
         <v>344</v>
       </c>
       <c r="B334" t="s">
+        <v>664</v>
+      </c>
+      <c r="C334" t="s">
         <v>665</v>
       </c>
-      <c r="C334" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="335" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="335" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A335">
         <v>345</v>
       </c>
       <c r="B335" t="s">
+        <v>666</v>
+      </c>
+      <c r="C335" t="s">
         <v>667</v>
       </c>
-      <c r="C335" t="s">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="336" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="336" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A336">
         <v>346</v>
       </c>
       <c r="B336" t="s">
+        <v>668</v>
+      </c>
+      <c r="C336" t="s">
         <v>669</v>
       </c>
-      <c r="C336" t="s">
-        <v>670</v>
-      </c>
-    </row>
-    <row r="337" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="337" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337">
         <v>347</v>
       </c>
       <c r="B337" t="s">
+        <v>670</v>
+      </c>
+      <c r="C337" t="s">
         <v>671</v>
       </c>
-      <c r="C337" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="338" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="338" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338">
         <v>348</v>
       </c>
       <c r="B338" t="s">
+        <v>672</v>
+      </c>
+      <c r="C338" t="s">
         <v>673</v>
       </c>
-      <c r="C338" t="s">
-        <v>674</v>
-      </c>
-    </row>
-    <row r="339" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="339" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A339">
         <v>349</v>
       </c>
       <c r="B339" t="s">
+        <v>674</v>
+      </c>
+      <c r="C339" t="s">
         <v>675</v>
       </c>
-      <c r="C339" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="340" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="340" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A340">
         <v>350</v>
       </c>
       <c r="B340" t="s">
+        <v>676</v>
+      </c>
+      <c r="C340" t="s">
         <v>677</v>
       </c>
-      <c r="C340" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="341" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="341" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341">
         <v>351</v>
       </c>
       <c r="B341" t="s">
+        <v>678</v>
+      </c>
+      <c r="C341" t="s">
         <v>679</v>
       </c>
-      <c r="C341" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="342" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="342" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A342">
         <v>352</v>
       </c>
       <c r="B342" t="s">
+        <v>680</v>
+      </c>
+      <c r="C342" t="s">
         <v>681</v>
       </c>
-      <c r="C342" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="343" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="343" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A343">
         <v>353</v>
       </c>
       <c r="B343" t="s">
+        <v>682</v>
+      </c>
+      <c r="C343" t="s">
         <v>683</v>
       </c>
-      <c r="C343" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="344" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="344" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A344">
         <v>354</v>
       </c>
       <c r="B344" t="s">
+        <v>684</v>
+      </c>
+      <c r="C344" t="s">
         <v>685</v>
       </c>
-      <c r="C344" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="345" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="345" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345">
         <v>355</v>
       </c>
       <c r="B345" t="s">
+        <v>686</v>
+      </c>
+      <c r="C345" t="s">
         <v>687</v>
       </c>
-      <c r="C345" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="346" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="346" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A346">
         <v>356</v>
       </c>
       <c r="B346" t="s">
+        <v>688</v>
+      </c>
+      <c r="C346" t="s">
         <v>689</v>
       </c>
-      <c r="C346" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="347" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="347" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347">
         <v>357</v>
       </c>
       <c r="B347" t="s">
+        <v>690</v>
+      </c>
+      <c r="C347" t="s">
         <v>691</v>
       </c>
-      <c r="C347" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="348" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="348" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A348">
         <v>358</v>
       </c>
       <c r="B348" t="s">
+        <v>692</v>
+      </c>
+      <c r="C348" t="s">
         <v>693</v>
       </c>
-      <c r="C348" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="349" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="349" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A349">
         <v>359</v>
       </c>
       <c r="B349" t="s">
+        <v>694</v>
+      </c>
+      <c r="C349" t="s">
         <v>695</v>
       </c>
-      <c r="C349" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="350" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="350" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A350">
         <v>360</v>
       </c>
       <c r="B350" t="s">
+        <v>696</v>
+      </c>
+      <c r="C350" t="s">
         <v>697</v>
       </c>
-      <c r="C350" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="351" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="351" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A351">
         <v>361</v>
       </c>
       <c r="B351" t="s">
+        <v>698</v>
+      </c>
+      <c r="C351" t="s">
         <v>699</v>
       </c>
-      <c r="C351" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="352" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="352" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A352">
         <v>362</v>
       </c>
       <c r="B352" t="s">
+        <v>700</v>
+      </c>
+      <c r="C352" t="s">
         <v>701</v>
       </c>
-      <c r="C352" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="353" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A353">
         <v>363</v>
       </c>
       <c r="B353" t="s">
+        <v>702</v>
+      </c>
+      <c r="C353" t="s">
         <v>703</v>
       </c>
-      <c r="C353" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="354" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A354">
         <v>364</v>
       </c>
       <c r="B354" t="s">
+        <v>704</v>
+      </c>
+      <c r="C354" t="s">
         <v>705</v>
       </c>
-      <c r="C354" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="355" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355">
         <v>365</v>
       </c>
       <c r="B355" t="s">
+        <v>706</v>
+      </c>
+      <c r="C355" t="s">
         <v>707</v>
       </c>
-      <c r="C355" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="356" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356">
         <v>366</v>
       </c>
       <c r="B356" t="s">
+        <v>708</v>
+      </c>
+      <c r="C356" t="s">
         <v>709</v>
       </c>
-      <c r="C356" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="357" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A357">
         <v>367</v>
       </c>
       <c r="B357" t="s">
+        <v>710</v>
+      </c>
+      <c r="C357" t="s">
         <v>711</v>
       </c>
-      <c r="C357" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="358" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358">
         <v>368</v>
       </c>
       <c r="B358" t="s">
+        <v>712</v>
+      </c>
+      <c r="C358" t="s">
         <v>713</v>
       </c>
-      <c r="C358" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="359" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A359">
         <v>369</v>
       </c>
       <c r="B359" t="s">
+        <v>714</v>
+      </c>
+      <c r="C359" t="s">
         <v>715</v>
       </c>
-      <c r="C359" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="360" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A360">
         <v>370</v>
       </c>
       <c r="B360" t="s">
+        <v>716</v>
+      </c>
+      <c r="C360" t="s">
         <v>717</v>
       </c>
-      <c r="C360" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="361" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A361">
         <v>371</v>
       </c>
       <c r="B361" t="s">
+        <v>718</v>
+      </c>
+      <c r="C361" t="s">
         <v>719</v>
       </c>
-      <c r="C361" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="362" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A362">
         <v>372</v>
       </c>
       <c r="B362" t="s">
+        <v>720</v>
+      </c>
+      <c r="C362" t="s">
         <v>721</v>
       </c>
-      <c r="C362" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="363" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363">
         <v>373</v>
       </c>
       <c r="B363" t="s">
+        <v>722</v>
+      </c>
+      <c r="C363" t="s">
         <v>723</v>
       </c>
-      <c r="C363" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="364" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A364">
         <v>374</v>
       </c>
       <c r="B364" t="s">
+        <v>724</v>
+      </c>
+      <c r="C364" t="s">
         <v>725</v>
       </c>
-      <c r="C364" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="365" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A365">
         <v>375</v>
       </c>
       <c r="B365" t="s">
+        <v>726</v>
+      </c>
+      <c r="C365" t="s">
         <v>727</v>
       </c>
-      <c r="C365" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="366" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A366">
         <v>376</v>
       </c>
       <c r="B366" t="s">
+        <v>728</v>
+      </c>
+      <c r="C366" t="s">
         <v>729</v>
       </c>
-      <c r="C366" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="367" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A367">
         <v>377</v>
       </c>
       <c r="B367" t="s">
+        <v>730</v>
+      </c>
+      <c r="C367" t="s">
         <v>731</v>
       </c>
-      <c r="C367" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="368" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368">
         <v>378</v>
       </c>
       <c r="B368" t="s">
+        <v>732</v>
+      </c>
+      <c r="C368" t="s">
         <v>733</v>
       </c>
-      <c r="C368" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="369" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="369" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A369">
         <v>379</v>
       </c>
       <c r="B369" t="s">
+        <v>734</v>
+      </c>
+      <c r="C369" t="s">
         <v>735</v>
       </c>
-      <c r="C369" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="370" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="370" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A370">
         <v>380</v>
       </c>
       <c r="B370" t="s">
+        <v>736</v>
+      </c>
+      <c r="C370" t="s">
         <v>737</v>
       </c>
-      <c r="C370" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="371" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="371" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371">
         <v>381</v>
       </c>
       <c r="B371" t="s">
+        <v>738</v>
+      </c>
+      <c r="C371" t="s">
         <v>739</v>
       </c>
-      <c r="C371" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="372" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="372" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372">
         <v>382</v>
       </c>
       <c r="B372" t="s">
+        <v>740</v>
+      </c>
+      <c r="C372" t="s">
         <v>741</v>
       </c>
-      <c r="C372" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="373" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="373" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A373">
         <v>383</v>
       </c>
       <c r="B373" t="s">
+        <v>742</v>
+      </c>
+      <c r="C373" t="s">
         <v>743</v>
       </c>
-      <c r="C373" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="374" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="374" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A374">
         <v>384</v>
       </c>
       <c r="B374" t="s">
+        <v>744</v>
+      </c>
+      <c r="C374" t="s">
         <v>745</v>
       </c>
-      <c r="C374" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="375" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="375" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A375">
         <v>385</v>
       </c>
       <c r="B375" t="s">
+        <v>746</v>
+      </c>
+      <c r="C375" t="s">
         <v>747</v>
       </c>
-      <c r="C375" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="376" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="376" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A376">
         <v>386</v>
       </c>
       <c r="B376" t="s">
+        <v>748</v>
+      </c>
+      <c r="C376" t="s">
         <v>749</v>
       </c>
-      <c r="C376" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="377" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="377" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A377">
         <v>387</v>
       </c>
       <c r="B377" t="s">
+        <v>750</v>
+      </c>
+      <c r="C377" t="s">
         <v>751</v>
       </c>
-      <c r="C377" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="378" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="378" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A378">
         <v>388</v>
       </c>
       <c r="B378" t="s">
+        <v>752</v>
+      </c>
+      <c r="C378" t="s">
         <v>753</v>
       </c>
-      <c r="C378" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="379" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="379" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379">
         <v>389</v>
       </c>
       <c r="B379" t="s">
+        <v>754</v>
+      </c>
+      <c r="C379" t="s">
         <v>755</v>
       </c>
-      <c r="C379" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="380" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="380" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A380">
         <v>390</v>
       </c>
       <c r="B380" t="s">
+        <v>756</v>
+      </c>
+      <c r="C380" t="s">
         <v>757</v>
       </c>
-      <c r="C380" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="381" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="381" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A381">
         <v>391</v>
       </c>
       <c r="B381" t="s">
+        <v>758</v>
+      </c>
+      <c r="C381" t="s">
         <v>759</v>
       </c>
-      <c r="C381" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="382" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="382" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A382">
         <v>392</v>
       </c>
       <c r="B382" t="s">
+        <v>760</v>
+      </c>
+      <c r="C382" t="s">
         <v>761</v>
       </c>
-      <c r="C382" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="383" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="383" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A383">
         <v>393</v>
       </c>
       <c r="B383" t="s">
+        <v>762</v>
+      </c>
+      <c r="C383" t="s">
         <v>763</v>
       </c>
-      <c r="C383" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="384" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="384" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A384">
         <v>394</v>
       </c>
       <c r="B384" t="s">
+        <v>764</v>
+      </c>
+      <c r="C384" t="s">
         <v>765</v>
       </c>
-      <c r="C384" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="385" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="385" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A385">
         <v>395</v>
       </c>
       <c r="B385" t="s">
+        <v>766</v>
+      </c>
+      <c r="C385" t="s">
         <v>767</v>
       </c>
-      <c r="C385" t="s">
-        <v>768</v>
-      </c>
-    </row>
-    <row r="386" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="386" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386">
         <v>396</v>
       </c>
       <c r="B386" t="s">
+        <v>768</v>
+      </c>
+      <c r="C386" t="s">
         <v>769</v>
       </c>
-      <c r="C386" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="387" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="387" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A387">
         <v>397</v>
       </c>
       <c r="B387" t="s">
+        <v>770</v>
+      </c>
+      <c r="C387" t="s">
         <v>771</v>
       </c>
-      <c r="C387" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="388" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="388" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A388">
         <v>398</v>
       </c>
       <c r="B388" t="s">
+        <v>772</v>
+      </c>
+      <c r="C388" t="s">
         <v>773</v>
       </c>
-      <c r="C388" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="389" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="389" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A389">
         <v>399</v>
       </c>
       <c r="B389" t="s">
+        <v>774</v>
+      </c>
+      <c r="C389" t="s">
         <v>775</v>
       </c>
-      <c r="C389" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="390" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="390" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390">
         <v>400</v>
       </c>
       <c r="B390" t="s">
+        <v>776</v>
+      </c>
+      <c r="C390" t="s">
         <v>777</v>
       </c>
-      <c r="C390" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="391" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="391" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A391">
         <v>401</v>
       </c>
       <c r="B391" t="s">
+        <v>778</v>
+      </c>
+      <c r="C391" t="s">
         <v>779</v>
       </c>
-      <c r="C391" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="392" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="392" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392">
         <v>402</v>
       </c>
       <c r="B392" t="s">
+        <v>780</v>
+      </c>
+      <c r="C392" t="s">
         <v>781</v>
       </c>
-      <c r="C392" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="393" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="393" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A393">
         <v>403</v>
       </c>
       <c r="B393" t="s">
+        <v>782</v>
+      </c>
+      <c r="C393" t="s">
         <v>783</v>
       </c>
-      <c r="C393" t="s">
-        <v>784</v>
-      </c>
-    </row>
-    <row r="394" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="394" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A394">
         <v>404</v>
       </c>
       <c r="B394" t="s">
+        <v>784</v>
+      </c>
+      <c r="C394" t="s">
         <v>785</v>
       </c>
-      <c r="C394" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="395" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="395" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A395">
         <v>405</v>
       </c>
       <c r="B395" t="s">
+        <v>786</v>
+      </c>
+      <c r="C395" t="s">
         <v>787</v>
       </c>
-      <c r="C395" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="396" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="396" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396">
         <v>406</v>
       </c>
       <c r="B396" t="s">
+        <v>788</v>
+      </c>
+      <c r="C396" t="s">
         <v>789</v>
       </c>
-      <c r="C396" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="397" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="397" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A397">
         <v>407</v>
       </c>
       <c r="B397" t="s">
+        <v>790</v>
+      </c>
+      <c r="C397" t="s">
         <v>791</v>
       </c>
-      <c r="C397" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="398" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="398" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A398">
         <v>408</v>
       </c>
       <c r="B398" t="s">
+        <v>792</v>
+      </c>
+      <c r="C398" t="s">
         <v>793</v>
       </c>
-      <c r="C398" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="399" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="399" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A399">
         <v>409</v>
       </c>
       <c r="B399" t="s">
+        <v>794</v>
+      </c>
+      <c r="C399" t="s">
         <v>795</v>
       </c>
-      <c r="C399" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="400" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="400" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A400">
         <v>410</v>
       </c>
       <c r="B400" t="s">
+        <v>796</v>
+      </c>
+      <c r="C400" t="s">
         <v>797</v>
       </c>
-      <c r="C400" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="401" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="401" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A401">
         <v>411</v>
       </c>
       <c r="B401" t="s">
+        <v>798</v>
+      </c>
+      <c r="C401" t="s">
         <v>799</v>
       </c>
-      <c r="C401" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="402" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="402" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A402">
         <v>412</v>
       </c>
       <c r="B402" t="s">
+        <v>800</v>
+      </c>
+      <c r="C402" t="s">
         <v>801</v>
       </c>
-      <c r="C402" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="403" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="403" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A403">
         <v>413</v>
       </c>
       <c r="B403" t="s">
+        <v>802</v>
+      </c>
+      <c r="C403" t="s">
         <v>803</v>
       </c>
-      <c r="C403" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="404" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="404" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A404">
         <v>414</v>
       </c>
       <c r="B404" t="s">
+        <v>804</v>
+      </c>
+      <c r="C404" t="s">
         <v>805</v>
       </c>
-      <c r="C404" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="405" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="405" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A405">
         <v>415</v>
       </c>
       <c r="B405" t="s">
+        <v>806</v>
+      </c>
+      <c r="C405" t="s">
         <v>807</v>
       </c>
-      <c r="C405" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="406" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="406" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A406">
         <v>416</v>
       </c>
       <c r="B406" t="s">
+        <v>808</v>
+      </c>
+      <c r="C406" t="s">
         <v>809</v>
       </c>
-      <c r="C406" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="407" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="407" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A407">
         <v>417</v>
       </c>
       <c r="B407" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="408" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="408" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A408">
         <v>418</v>
       </c>
       <c r="B408" t="s">
+        <v>811</v>
+      </c>
+      <c r="C408" t="s">
         <v>812</v>
       </c>
-      <c r="C408" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="409" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="409" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A409">
         <v>419</v>
       </c>
       <c r="B409" t="s">
+        <v>813</v>
+      </c>
+      <c r="C409" t="s">
         <v>814</v>
       </c>
-      <c r="C409" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="410" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="410" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A410">
         <v>420</v>
       </c>
       <c r="B410" t="s">
+        <v>815</v>
+      </c>
+      <c r="C410" t="s">
         <v>816</v>
       </c>
-      <c r="C410" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="411" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="411" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A411">
         <v>421</v>
       </c>
       <c r="B411" t="s">
+        <v>817</v>
+      </c>
+      <c r="C411" t="s">
         <v>818</v>
       </c>
-      <c r="C411" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="412" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="412" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A412">
         <v>422</v>
       </c>
       <c r="B412" t="s">
+        <v>819</v>
+      </c>
+      <c r="C412" t="s">
         <v>820</v>
       </c>
-      <c r="C412" t="s">
-        <v>821</v>
-      </c>
-    </row>
-    <row r="413" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="413" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A413">
         <v>423</v>
       </c>
       <c r="B413" t="s">
+        <v>821</v>
+      </c>
+      <c r="C413" t="s">
         <v>822</v>
       </c>
-      <c r="C413" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="414" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="414" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A414">
         <v>424</v>
       </c>
       <c r="B414" t="s">
+        <v>823</v>
+      </c>
+      <c r="C414" t="s">
         <v>824</v>
       </c>
-      <c r="C414" t="s">
-        <v>825</v>
-      </c>
-    </row>
-    <row r="415" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="415" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A415">
         <v>425</v>
       </c>
       <c r="B415" t="s">
+        <v>825</v>
+      </c>
+      <c r="C415" t="s">
         <v>826</v>
       </c>
-      <c r="C415" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="416" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="416" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A416">
         <v>426</v>
       </c>
       <c r="B416" t="s">
+        <v>827</v>
+      </c>
+      <c r="C416" t="s">
         <v>828</v>
       </c>
-      <c r="C416" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="417" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A417">
         <v>427</v>
       </c>
       <c r="B417" t="s">
+        <v>829</v>
+      </c>
+      <c r="C417" t="s">
         <v>830</v>
       </c>
-      <c r="C417" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="418" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A418">
         <v>428</v>
       </c>
       <c r="B418" t="s">
+        <v>831</v>
+      </c>
+      <c r="C418" t="s">
         <v>832</v>
       </c>
-      <c r="C418" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="419" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A419">
         <v>429</v>
       </c>
       <c r="B419" t="s">
+        <v>833</v>
+      </c>
+      <c r="C419" t="s">
         <v>834</v>
       </c>
-      <c r="C419" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="420" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A420">
         <v>430</v>
       </c>
       <c r="B420" t="s">
+        <v>835</v>
+      </c>
+      <c r="C420" t="s">
         <v>836</v>
       </c>
-      <c r="C420" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="421" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A421">
         <v>431</v>
       </c>
       <c r="B421" t="s">
+        <v>837</v>
+      </c>
+      <c r="C421" t="s">
         <v>838</v>
       </c>
-      <c r="C421" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="422" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A422">
         <v>432</v>
       </c>
       <c r="B422" t="s">
+        <v>839</v>
+      </c>
+      <c r="C422" t="s">
         <v>840</v>
       </c>
-      <c r="C422" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="423" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A423">
         <v>433</v>
       </c>
       <c r="B423" t="s">
+        <v>841</v>
+      </c>
+      <c r="C423" t="s">
         <v>842</v>
       </c>
-      <c r="C423" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="424" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A424">
         <v>434</v>
       </c>
       <c r="B424" t="s">
+        <v>843</v>
+      </c>
+      <c r="C424" t="s">
         <v>844</v>
       </c>
-      <c r="C424" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="425" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A425">
         <v>435</v>
       </c>
       <c r="B425" t="s">
+        <v>845</v>
+      </c>
+      <c r="C425" t="s">
         <v>846</v>
       </c>
-      <c r="C425" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="426" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A426">
         <v>436</v>
       </c>
       <c r="B426" t="s">
+        <v>847</v>
+      </c>
+      <c r="C426" t="s">
         <v>848</v>
       </c>
-      <c r="C426" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="427" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A427">
         <v>437</v>
       </c>
       <c r="B427" t="s">
+        <v>849</v>
+      </c>
+      <c r="C427" t="s">
         <v>850</v>
       </c>
-      <c r="C427" t="s">
-        <v>851</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="428" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A428">
         <v>438</v>
       </c>
       <c r="B428" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C428" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="429" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A429">
         <v>439</v>
       </c>
       <c r="B429" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C429" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="430" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A430">
         <v>440</v>
       </c>
       <c r="B430" t="s">
+        <v>853</v>
+      </c>
+      <c r="C430" t="s">
         <v>854</v>
       </c>
-      <c r="C430" t="s">
-        <v>855</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="431" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A431">
         <v>441</v>
       </c>
       <c r="B431" t="s">
+        <v>855</v>
+      </c>
+      <c r="C431" t="s">
         <v>856</v>
       </c>
-      <c r="C431" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="432" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A432">
         <v>442</v>
       </c>
       <c r="B432" t="s">
+        <v>857</v>
+      </c>
+      <c r="C432" t="s">
         <v>858</v>
       </c>
-      <c r="C432" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="433" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="433" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A433">
         <v>443</v>
       </c>
       <c r="B433" t="s">
+        <v>859</v>
+      </c>
+      <c r="C433" t="s">
         <v>860</v>
       </c>
-      <c r="C433" t="s">
-        <v>861</v>
-      </c>
-    </row>
-    <row r="434" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="434" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A434">
         <v>444</v>
       </c>
       <c r="B434" t="s">
+        <v>861</v>
+      </c>
+      <c r="C434" t="s">
         <v>862</v>
       </c>
-      <c r="C434" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="435" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="435" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A435">
         <v>445</v>
       </c>
       <c r="B435" t="s">
+        <v>863</v>
+      </c>
+      <c r="C435" t="s">
         <v>864</v>
       </c>
-      <c r="C435" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="436" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="436" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A436">
         <v>446</v>
       </c>
       <c r="B436" t="s">
+        <v>865</v>
+      </c>
+      <c r="C436" t="s">
         <v>866</v>
       </c>
-      <c r="C436" t="s">
-        <v>867</v>
-      </c>
-    </row>
-    <row r="437" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="437" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A437">
         <v>447</v>
       </c>
       <c r="B437" t="s">
+        <v>867</v>
+      </c>
+      <c r="C437" t="s">
         <v>868</v>
       </c>
-      <c r="C437" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="438" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="438" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A438">
         <v>448</v>
       </c>
       <c r="B438" t="s">
+        <v>869</v>
+      </c>
+      <c r="C438" t="s">
         <v>870</v>
       </c>
-      <c r="C438" t="s">
-        <v>871</v>
-      </c>
-    </row>
-    <row r="439" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="439" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A439">
         <v>449</v>
       </c>
       <c r="B439" t="s">
+        <v>871</v>
+      </c>
+      <c r="C439" t="s">
         <v>872</v>
       </c>
-      <c r="C439" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="440" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="440" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A440">
         <v>450</v>
       </c>
       <c r="B440" t="s">
+        <v>873</v>
+      </c>
+      <c r="C440" t="s">
         <v>874</v>
       </c>
-      <c r="C440" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="441" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="441" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A441">
         <v>451</v>
       </c>
       <c r="B441" t="s">
+        <v>875</v>
+      </c>
+      <c r="C441" t="s">
         <v>876</v>
       </c>
-      <c r="C441" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="442" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="442" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A442">
         <v>452</v>
       </c>
       <c r="B442" t="s">
+        <v>877</v>
+      </c>
+      <c r="C442" t="s">
         <v>878</v>
       </c>
-      <c r="C442" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="443" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="443" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A443">
         <v>453</v>
       </c>
       <c r="B443" t="s">
+        <v>879</v>
+      </c>
+      <c r="C443" t="s">
         <v>880</v>
       </c>
-      <c r="C443" t="s">
-        <v>881</v>
-      </c>
-    </row>
-    <row r="444" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="444" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A444">
         <v>455</v>
       </c>
       <c r="B444" t="s">
+        <v>881</v>
+      </c>
+      <c r="C444" t="s">
         <v>882</v>
       </c>
-      <c r="C444" t="s">
-        <v>883</v>
-      </c>
-    </row>
-    <row r="445" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="445" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A445">
         <v>456</v>
       </c>
       <c r="B445" t="s">
+        <v>883</v>
+      </c>
+      <c r="C445" t="s">
         <v>884</v>
       </c>
-      <c r="C445" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="446" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="446" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A446">
         <v>457</v>
       </c>
       <c r="B446" t="s">
+        <v>885</v>
+      </c>
+      <c r="C446" t="s">
         <v>886</v>
       </c>
-      <c r="C446" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="447" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="447" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A447">
         <v>458</v>
       </c>
       <c r="B447" t="s">
+        <v>887</v>
+      </c>
+      <c r="C447" t="s">
         <v>888</v>
       </c>
-      <c r="C447" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="448" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="448" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A448">
         <v>459</v>
       </c>
       <c r="B448" t="s">
+        <v>889</v>
+      </c>
+      <c r="C448" t="s">
         <v>890</v>
       </c>
-      <c r="C448" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="449" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="449" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A449">
         <v>460</v>
       </c>
       <c r="B449" t="s">
+        <v>891</v>
+      </c>
+      <c r="C449" t="s">
         <v>892</v>
       </c>
-      <c r="C449" t="s">
-        <v>893</v>
-      </c>
-    </row>
-    <row r="450" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="450" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A450">
         <v>461</v>
       </c>
       <c r="B450" t="s">
+        <v>893</v>
+      </c>
+      <c r="C450" t="s">
         <v>894</v>
       </c>
-      <c r="C450" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="451" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="451" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A451">
         <v>462</v>
       </c>
       <c r="B451" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C451" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="452" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="452" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A452">
         <v>463</v>
       </c>
       <c r="B452" t="s">
+        <v>896</v>
+      </c>
+      <c r="C452" t="s">
         <v>897</v>
       </c>
-      <c r="C452" t="s">
-        <v>898</v>
-      </c>
-    </row>
-    <row r="453" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="453" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A453">
         <v>464</v>
       </c>
       <c r="B453" t="s">
+        <v>898</v>
+      </c>
+      <c r="C453" t="s">
         <v>899</v>
       </c>
-      <c r="C453" t="s">
-        <v>900</v>
-      </c>
-    </row>
-    <row r="454" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="454" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A454">
         <v>465</v>
       </c>
       <c r="B454" t="s">
+        <v>900</v>
+      </c>
+      <c r="C454" t="s">
         <v>901</v>
       </c>
-      <c r="C454" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="455" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="455" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A455">
         <v>466</v>
       </c>
       <c r="B455" t="s">
+        <v>902</v>
+      </c>
+      <c r="C455" t="s">
         <v>903</v>
       </c>
-      <c r="C455" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="456" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="456" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A456">
         <v>467</v>
       </c>
       <c r="B456" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C456" t="s">
-        <v>905</v>
-      </c>
-    </row>
-    <row r="457" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="457" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A457">
         <v>468</v>
       </c>
       <c r="B457" t="s">
+        <v>905</v>
+      </c>
+      <c r="C457" t="s">
         <v>906</v>
       </c>
-      <c r="C457" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="458" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="458" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A458">
         <v>469</v>
       </c>
       <c r="B458" t="s">
+        <v>907</v>
+      </c>
+      <c r="C458" t="s">
         <v>908</v>
       </c>
-      <c r="C458" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="459" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="459" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A459">
         <v>470</v>
       </c>
       <c r="B459" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="460" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="460" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A460">
         <v>471</v>
       </c>
       <c r="B460" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="461" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="461" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A461">
         <v>472</v>
       </c>
       <c r="B461" t="s">
+        <v>911</v>
+      </c>
+      <c r="C461" t="s">
         <v>912</v>
       </c>
-      <c r="C461" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="462" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="462" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A462">
         <v>473</v>
       </c>
       <c r="B462" t="s">
+        <v>913</v>
+      </c>
+      <c r="C462" t="s">
         <v>914</v>
       </c>
-      <c r="C462" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="463" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="463" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A463">
         <v>474</v>
       </c>
       <c r="B463" t="s">
+        <v>915</v>
+      </c>
+      <c r="C463" t="s">
         <v>916</v>
       </c>
-      <c r="C463" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="464" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="464" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A464">
         <v>475</v>
       </c>
       <c r="B464" t="s">
+        <v>917</v>
+      </c>
+      <c r="C464" t="s">
         <v>918</v>
       </c>
-      <c r="C464" t="s">
-        <v>919</v>
-      </c>
-    </row>
-    <row r="465" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="465" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A465">
         <v>476</v>
       </c>
       <c r="B465" t="s">
+        <v>919</v>
+      </c>
+      <c r="C465" t="s">
         <v>920</v>
       </c>
-      <c r="C465" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="466" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="466" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A466">
         <v>477</v>
       </c>
       <c r="B466" t="s">
+        <v>921</v>
+      </c>
+      <c r="C466" t="s">
         <v>922</v>
       </c>
-      <c r="C466" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="467" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="467" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A467">
         <v>478</v>
       </c>
       <c r="B467" t="s">
+        <v>923</v>
+      </c>
+      <c r="C467" t="s">
         <v>924</v>
       </c>
-      <c r="C467" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="468" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="468" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A468">
         <v>479</v>
       </c>
       <c r="B468" t="s">
+        <v>925</v>
+      </c>
+      <c r="C468" t="s">
         <v>926</v>
       </c>
-      <c r="C468" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="469" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="469" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A469">
         <v>480</v>
       </c>
       <c r="B469" t="s">
+        <v>927</v>
+      </c>
+      <c r="C469" t="s">
         <v>928</v>
       </c>
-      <c r="C469" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="470" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="470" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A470">
         <v>481</v>
       </c>
       <c r="B470" t="s">
+        <v>929</v>
+      </c>
+      <c r="C470" t="s">
         <v>930</v>
       </c>
-      <c r="C470" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="471" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="471" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A471">
         <v>482</v>
       </c>
       <c r="B471" t="s">
+        <v>931</v>
+      </c>
+      <c r="C471" t="s">
         <v>932</v>
       </c>
-      <c r="C471" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="472" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="472" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A472">
         <v>483</v>
       </c>
       <c r="B472" t="s">
+        <v>933</v>
+      </c>
+      <c r="C472" t="s">
         <v>934</v>
       </c>
-      <c r="C472" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="473" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="473" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A473">
         <v>484</v>
       </c>
       <c r="B473" t="s">
+        <v>935</v>
+      </c>
+      <c r="C473" t="s">
         <v>936</v>
       </c>
-      <c r="C473" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="474" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="474" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A474">
         <v>485</v>
       </c>
       <c r="B474" t="s">
+        <v>937</v>
+      </c>
+      <c r="C474" t="s">
         <v>938</v>
       </c>
-      <c r="C474" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="475" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="475" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A475">
         <v>486</v>
       </c>
       <c r="B475" t="s">
+        <v>939</v>
+      </c>
+      <c r="C475" t="s">
         <v>940</v>
       </c>
-      <c r="C475" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="476" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="476" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A476">
         <v>487</v>
       </c>
       <c r="B476" t="s">
+        <v>941</v>
+      </c>
+      <c r="C476" t="s">
         <v>942</v>
       </c>
-      <c r="C476" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="477" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="477" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A477">
         <v>488</v>
       </c>
       <c r="B477" t="s">
+        <v>943</v>
+      </c>
+      <c r="C477" t="s">
         <v>944</v>
       </c>
-      <c r="C477" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="478" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="478" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A478">
         <v>489</v>
       </c>
       <c r="B478" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="C478" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="479" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="479" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A479">
         <v>490</v>
       </c>
       <c r="B479" t="s">
+        <v>946</v>
+      </c>
+      <c r="C479" t="s">
         <v>947</v>
       </c>
-      <c r="C479" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="480" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="480" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A480">
         <v>491</v>
       </c>
       <c r="B480" t="s">
+        <v>948</v>
+      </c>
+      <c r="C480" t="s">
         <v>949</v>
       </c>
-      <c r="C480" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="481" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="481" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A481">
         <v>492</v>
       </c>
       <c r="B481" t="s">
+        <v>950</v>
+      </c>
+      <c r="C481" t="s">
         <v>951</v>
       </c>
-      <c r="C481" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="482" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="482" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A482">
         <v>493</v>
       </c>
       <c r="B482" t="s">
+        <v>952</v>
+      </c>
+      <c r="C482" t="s">
         <v>953</v>
       </c>
-      <c r="C482" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="483" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="483" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A483">
         <v>494</v>
       </c>
       <c r="B483" t="s">
+        <v>954</v>
+      </c>
+      <c r="C483" t="s">
         <v>955</v>
       </c>
-      <c r="C483" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="484" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="484" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A484">
         <v>496</v>
       </c>
       <c r="B484" t="s">
+        <v>956</v>
+      </c>
+      <c r="C484" t="s">
         <v>957</v>
       </c>
-      <c r="C484" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="485" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="485" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A485">
         <v>497</v>
       </c>
       <c r="B485" t="s">
+        <v>958</v>
+      </c>
+      <c r="C485" t="s">
         <v>959</v>
       </c>
-      <c r="C485" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="486" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="486" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A486">
         <v>498</v>
       </c>
       <c r="B486" t="s">
+        <v>960</v>
+      </c>
+      <c r="C486" t="s">
         <v>961</v>
       </c>
-      <c r="C486" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="487" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="487" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A487">
         <v>499</v>
       </c>
       <c r="B487" t="s">
+        <v>962</v>
+      </c>
+      <c r="C487" t="s">
         <v>963</v>
       </c>
-      <c r="C487" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="488" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="488" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A488">
         <v>500</v>
       </c>
       <c r="B488" t="s">
+        <v>964</v>
+      </c>
+      <c r="C488" t="s">
         <v>965</v>
       </c>
-      <c r="C488" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="489" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="489" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A489">
         <v>501</v>
       </c>
       <c r="B489" t="s">
+        <v>966</v>
+      </c>
+      <c r="C489" t="s">
         <v>967</v>
       </c>
-      <c r="C489" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="490" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="490" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A490">
         <v>502</v>
       </c>
       <c r="B490" t="s">
+        <v>968</v>
+      </c>
+      <c r="C490" t="s">
         <v>969</v>
       </c>
-      <c r="C490" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="491" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="491" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A491">
         <v>503</v>
       </c>
       <c r="B491" t="s">
+        <v>970</v>
+      </c>
+      <c r="C491" t="s">
         <v>971</v>
       </c>
-      <c r="C491" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="492" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="492" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A492">
         <v>504</v>
       </c>
       <c r="B492" t="s">
+        <v>972</v>
+      </c>
+      <c r="C492" t="s">
         <v>973</v>
       </c>
-      <c r="C492" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="493" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="493" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A493">
         <v>505</v>
       </c>
       <c r="B493" t="s">
+        <v>974</v>
+      </c>
+      <c r="C493" t="s">
         <v>975</v>
       </c>
-      <c r="C493" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="494" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="494" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A494">
         <v>506</v>
       </c>
       <c r="B494" t="s">
+        <v>976</v>
+      </c>
+      <c r="C494" t="s">
         <v>977</v>
       </c>
-      <c r="C494" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="495" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="495" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A495">
         <v>507</v>
       </c>
       <c r="B495" t="s">
+        <v>978</v>
+      </c>
+      <c r="C495" t="s">
         <v>979</v>
       </c>
-      <c r="C495" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="496" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="496" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A496">
         <v>508</v>
       </c>
       <c r="B496" t="s">
+        <v>980</v>
+      </c>
+      <c r="C496" t="s">
         <v>981</v>
       </c>
-      <c r="C496" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="497" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="497" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A497">
         <v>509</v>
       </c>
       <c r="B497" t="s">
+        <v>982</v>
+      </c>
+      <c r="C497" t="s">
         <v>983</v>
       </c>
-      <c r="C497" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="498" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="498" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A498">
         <v>510</v>
       </c>
       <c r="B498" t="s">
+        <v>984</v>
+      </c>
+      <c r="C498" t="s">
         <v>985</v>
       </c>
-      <c r="C498" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="499" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="499" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A499">
         <v>511</v>
       </c>
       <c r="B499" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="500" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="500" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A500">
         <v>512</v>
       </c>
       <c r="B500" t="s">
+        <v>987</v>
+      </c>
+      <c r="C500" t="s">
         <v>988</v>
       </c>
-      <c r="C500" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="501" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="501" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A501">
         <v>513</v>
       </c>
       <c r="B501" t="s">
+        <v>989</v>
+      </c>
+      <c r="C501" t="s">
         <v>990</v>
       </c>
-      <c r="C501" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="502" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="502" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A502">
         <v>514</v>
       </c>
       <c r="B502" t="s">
+        <v>991</v>
+      </c>
+      <c r="C502" t="s">
         <v>992</v>
       </c>
-      <c r="C502" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="503" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="503" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A503">
         <v>515</v>
       </c>
       <c r="B503" t="s">
+        <v>993</v>
+      </c>
+      <c r="C503" t="s">
         <v>994</v>
       </c>
-      <c r="C503" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="504" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="504" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A504">
         <v>516</v>
       </c>
       <c r="B504" t="s">
+        <v>995</v>
+      </c>
+      <c r="C504" t="s">
         <v>996</v>
       </c>
-      <c r="C504" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="505" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="505" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A505">
         <v>517</v>
       </c>
       <c r="B505" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="506" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="506" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A506">
         <v>518</v>
       </c>
       <c r="B506" t="s">
+        <v>998</v>
+      </c>
+      <c r="C506" t="s">
         <v>999</v>
       </c>
-      <c r="C506" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="507" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="507" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A507">
         <v>519</v>
       </c>
       <c r="B507" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C507" t="s">
         <v>1001</v>
       </c>
-      <c r="C507" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="508" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="508" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A508">
         <v>520</v>
       </c>
       <c r="B508" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C508" t="s">
         <v>1003</v>
       </c>
-      <c r="C508" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="509" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="509" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A509">
         <v>521</v>
       </c>
       <c r="B509" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C509" t="s">
         <v>1005</v>
       </c>
-      <c r="C509" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="510" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="510" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A510">
         <v>522</v>
       </c>
       <c r="B510" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C510" t="s">
         <v>1007</v>
       </c>
-      <c r="C510" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="511" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="511" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A511">
         <v>523</v>
       </c>
       <c r="B511" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C511" t="s">
         <v>1009</v>
       </c>
-      <c r="C511" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="512" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="512" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A512">
         <v>524</v>
       </c>
       <c r="B512" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C512" t="s">
         <v>1011</v>
       </c>
-      <c r="C512" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="513" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="513" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A513">
         <v>525</v>
       </c>
       <c r="B513" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C513" t="s">
         <v>1013</v>
       </c>
-      <c r="C513" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="514" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="514" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A514">
         <v>526</v>
       </c>
       <c r="B514" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C514" t="s">
         <v>1015</v>
       </c>
-      <c r="C514" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="515" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="515" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A515">
         <v>527</v>
       </c>
       <c r="B515" t="s">
+        <v>1016</v>
+      </c>
+      <c r="C515" t="s">
         <v>1017</v>
       </c>
-      <c r="C515" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="516" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="516" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A516">
         <v>528</v>
       </c>
       <c r="B516" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C516" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="517" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="517" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A517">
         <v>529</v>
       </c>
       <c r="B517" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C517" t="s">
         <v>1020</v>
       </c>
-      <c r="C517" t="s">
-        <v>1021</v>
-      </c>
-    </row>
-    <row r="518" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="518" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A518">
         <v>530</v>
       </c>
       <c r="B518" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="519" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="519" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A519">
         <v>531</v>
       </c>
       <c r="B519" t="s">
+        <v>1022</v>
+      </c>
+      <c r="C519" t="s">
         <v>1023</v>
       </c>
-      <c r="C519" t="s">
-        <v>1024</v>
-      </c>
-    </row>
-    <row r="520" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="520" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A520">
         <v>532</v>
       </c>
       <c r="B520" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C520" t="s">
         <v>1025</v>
       </c>
-      <c r="C520" t="s">
-        <v>1026</v>
-      </c>
-    </row>
-    <row r="521" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="521" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A521">
         <v>533</v>
       </c>
       <c r="B521" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C521" t="s">
         <v>1027</v>
       </c>
-      <c r="C521" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="522" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="522" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A522">
         <v>534</v>
       </c>
       <c r="B522" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C522" t="s">
         <v>1029</v>
       </c>
-      <c r="C522" t="s">
-        <v>1030</v>
-      </c>
-    </row>
-    <row r="523" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="523" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A523">
         <v>535</v>
       </c>
       <c r="B523" t="s">
+        <v>1030</v>
+      </c>
+      <c r="C523" t="s">
         <v>1031</v>
       </c>
-      <c r="C523" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="524" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="524" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A524">
         <v>536</v>
       </c>
       <c r="B524" t="s">
+        <v>1032</v>
+      </c>
+      <c r="C524" t="s">
         <v>1033</v>
       </c>
-      <c r="C524" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="525" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="525" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A525">
         <v>537</v>
       </c>
       <c r="B525" t="s">
+        <v>1034</v>
+      </c>
+      <c r="C525" t="s">
         <v>1035</v>
       </c>
-      <c r="C525" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="526" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="526" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A526">
         <v>538</v>
       </c>
       <c r="B526" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C526" t="s">
         <v>1037</v>
       </c>
-      <c r="C526" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="527" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="527" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A527">
         <v>539</v>
       </c>
       <c r="B527" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C527" t="s">
         <v>1039</v>
       </c>
-      <c r="C527" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="528" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="528" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A528">
         <v>540</v>
       </c>
       <c r="B528" t="s">
+        <v>1040</v>
+      </c>
+      <c r="C528" t="s">
         <v>1041</v>
       </c>
-      <c r="C528" t="s">
-        <v>1042</v>
-      </c>
-    </row>
-    <row r="529" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="529" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A529">
         <v>542</v>
       </c>
       <c r="B529" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C529" t="s">
         <v>1043</v>
       </c>
-      <c r="C529" t="s">
-        <v>1044</v>
-      </c>
-    </row>
-    <row r="530" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="530" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A530">
         <v>543</v>
       </c>
       <c r="B530" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C530" t="s">
         <v>1045</v>
       </c>
-      <c r="C530" t="s">
-        <v>1046</v>
-      </c>
-    </row>
-    <row r="531" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="531" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A531">
         <v>545</v>
       </c>
       <c r="B531" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C531" t="s">
         <v>1047</v>
       </c>
-      <c r="C531" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="532" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="532" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A532">
         <v>546</v>
       </c>
       <c r="B532" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C532" t="s">
         <v>1049</v>
       </c>
-      <c r="C532" t="s">
-        <v>1050</v>
-      </c>
-    </row>
-    <row r="533" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="533" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A533">
         <v>547</v>
       </c>
       <c r="B533" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C533" t="s">
         <v>1051</v>
       </c>
-      <c r="C533" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="534" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="534" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A534">
         <v>548</v>
       </c>
       <c r="B534" t="s">
+        <v>1052</v>
+      </c>
+      <c r="C534" t="s">
         <v>1053</v>
       </c>
-      <c r="C534" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="535" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="535" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A535">
         <v>549</v>
       </c>
       <c r="B535" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C535" t="s">
         <v>1055</v>
       </c>
-      <c r="C535" t="s">
-        <v>1056</v>
-      </c>
-    </row>
-    <row r="536" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="536" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A536">
         <v>550</v>
       </c>
       <c r="B536" t="s">
+        <v>1056</v>
+      </c>
+      <c r="C536" t="s">
         <v>1057</v>
       </c>
-      <c r="C536" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="537" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="537" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A537">
         <v>551</v>
       </c>
       <c r="B537" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="538" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="538" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A538">
         <v>552</v>
       </c>
       <c r="B538" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C538" t="s">
         <v>1060</v>
       </c>
-      <c r="C538" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="539" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="539" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A539">
         <v>553</v>
       </c>
       <c r="B539" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C539" t="s">
         <v>1062</v>
       </c>
-      <c r="C539" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="540" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="540" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A540">
         <v>554</v>
       </c>
       <c r="B540" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C540" t="s">
         <v>1064</v>
       </c>
-      <c r="C540" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="541" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="541" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A541">
         <v>555</v>
       </c>
       <c r="B541" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C541" t="s">
         <v>1066</v>
       </c>
-      <c r="C541" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="542" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="542" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A542">
         <v>556</v>
       </c>
       <c r="B542" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C542" t="s">
         <v>1068</v>
       </c>
-      <c r="C542" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="543" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="543" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A543">
         <v>557</v>
       </c>
       <c r="B543" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C543" t="s">
         <v>1070</v>
       </c>
-      <c r="C543" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="544" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="544" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A544">
         <v>558</v>
       </c>
       <c r="B544" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C544" t="s">
         <v>1072</v>
       </c>
-      <c r="C544" t="s">
-        <v>1073</v>
-      </c>
-    </row>
-    <row r="545" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="545" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A545">
         <v>559</v>
       </c>
       <c r="B545" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C545" t="s">
         <v>1074</v>
       </c>
-      <c r="C545" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="546" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="546" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A546">
         <v>562</v>
       </c>
       <c r="B546" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C546" t="s">
         <v>1076</v>
       </c>
-      <c r="C546" t="s">
-        <v>1077</v>
-      </c>
-    </row>
-    <row r="547" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="547" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A547">
         <v>563</v>
       </c>
       <c r="B547" t="s">
-        <v>1078</v>
-      </c>
-    </row>
-    <row r="548" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A548">
         <v>564</v>
       </c>
       <c r="B548" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C548" t="s">
         <v>1079</v>
       </c>
-      <c r="C548" t="s">
-        <v>1080</v>
-      </c>
-    </row>
-    <row r="549" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="549" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A549">
         <v>565</v>
       </c>
       <c r="B549" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C549" t="s">
         <v>1081</v>
       </c>
-      <c r="C549" t="s">
-        <v>1082</v>
-      </c>
-    </row>
-    <row r="550" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="550" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A550">
         <v>566</v>
       </c>
       <c r="B550" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C550" t="s">
         <v>1083</v>
       </c>
-      <c r="C550" t="s">
-        <v>1084</v>
-      </c>
-    </row>
-    <row r="551" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="551" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A551">
         <v>567</v>
       </c>
       <c r="B551" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C551" t="s">
         <v>1085</v>
       </c>
-      <c r="C551" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="552" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="552" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A552">
         <v>568</v>
       </c>
       <c r="B552" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C552" t="s">
         <v>1087</v>
       </c>
-      <c r="C552" t="s">
-        <v>1088</v>
-      </c>
-    </row>
-    <row r="553" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="553" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A553">
         <v>569</v>
       </c>
       <c r="B553" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C553" t="s">
         <v>1089</v>
       </c>
-      <c r="C553" t="s">
-        <v>1090</v>
-      </c>
-    </row>
-    <row r="554" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="554" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A554">
         <v>570</v>
       </c>
       <c r="B554" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C554" t="s">
         <v>1091</v>
       </c>
-      <c r="C554" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="555" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="555" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A555">
         <v>571</v>
       </c>
       <c r="B555" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C555" t="s">
         <v>1093</v>
       </c>
-      <c r="C555" t="s">
-        <v>1094</v>
-      </c>
-    </row>
-    <row r="556" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="556" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A556">
         <v>572</v>
       </c>
       <c r="B556" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="557" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1094</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A557">
         <v>577</v>
       </c>
       <c r="B557" t="s">
-        <v>1096</v>
-      </c>
-    </row>
-    <row r="558" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A558">
         <v>578</v>
       </c>
       <c r="B558" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C558" t="s">
         <v>1097</v>
       </c>
-      <c r="C558" t="s">
-        <v>1098</v>
-      </c>
-    </row>
-    <row r="559" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="559" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A559">
         <v>579</v>
       </c>
       <c r="B559" t="s">
-        <v>1099</v>
-      </c>
-    </row>
-    <row r="560" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A560">
         <v>580</v>
       </c>
       <c r="B560" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C560" t="s">
         <v>1100</v>
       </c>
-      <c r="C560" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="561" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="561" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A561">
         <v>581</v>
       </c>
       <c r="B561" t="s">
+        <v>1101</v>
+      </c>
+      <c r="C561" t="s">
         <v>1102</v>
       </c>
-      <c r="C561" t="s">
-        <v>1103</v>
-      </c>
-    </row>
-    <row r="562" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="562" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A562">
         <v>582</v>
       </c>
       <c r="B562" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C562" t="s">
         <v>1104</v>
       </c>
-      <c r="C562" t="s">
-        <v>1105</v>
-      </c>
-    </row>
-    <row r="563" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="563" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A563">
         <v>583</v>
       </c>
       <c r="B563" t="s">
+        <v>1105</v>
+      </c>
+      <c r="C563" t="s">
         <v>1106</v>
       </c>
-      <c r="C563" t="s">
-        <v>1107</v>
-      </c>
-    </row>
-    <row r="564" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="564" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A564">
         <v>584</v>
       </c>
       <c r="B564" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C564" t="s">
         <v>1108</v>
       </c>
-      <c r="C564" t="s">
-        <v>1109</v>
-      </c>
-    </row>
-    <row r="565" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="565" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A565">
         <v>585</v>
       </c>
       <c r="B565" t="s">
-        <v>1110</v>
-      </c>
-    </row>
-    <row r="566" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="566" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A566">
         <v>586</v>
       </c>
       <c r="B566" t="s">
+        <v>1110</v>
+      </c>
+      <c r="C566" t="s">
         <v>1111</v>
       </c>
-      <c r="C566" t="s">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="567" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="567" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A567">
         <v>587</v>
       </c>
       <c r="B567" t="s">
+        <v>1112</v>
+      </c>
+      <c r="C567" t="s">
         <v>1113</v>
       </c>
-      <c r="C567" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="568" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="568" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A568">
         <v>588</v>
       </c>
       <c r="B568" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C568" t="s">
         <v>1115</v>
       </c>
-      <c r="C568" t="s">
-        <v>1116</v>
-      </c>
-    </row>
-    <row r="569" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="569" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A569">
         <v>589</v>
       </c>
       <c r="B569" t="s">
+        <v>1116</v>
+      </c>
+      <c r="C569" t="s">
         <v>1117</v>
       </c>
-      <c r="C569" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="570" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="570" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A570">
         <v>590</v>
       </c>
       <c r="B570" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C570" t="s">
         <v>1119</v>
       </c>
-      <c r="C570" t="s">
-        <v>1120</v>
-      </c>
-    </row>
-    <row r="571" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="571" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A571">
         <v>591</v>
       </c>
       <c r="B571" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C571" t="s">
         <v>1121</v>
       </c>
-      <c r="C571" t="s">
-        <v>1122</v>
-      </c>
-    </row>
-    <row r="572" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="572" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A572">
         <v>592</v>
       </c>
       <c r="B572" t="s">
+        <v>1122</v>
+      </c>
+      <c r="C572" t="s">
         <v>1123</v>
       </c>
-      <c r="C572" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="573" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="573" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A573">
         <v>593</v>
       </c>
       <c r="B573" t="s">
+        <v>1124</v>
+      </c>
+      <c r="C573" t="s">
         <v>1125</v>
       </c>
-      <c r="C573" t="s">
-        <v>1126</v>
-      </c>
-    </row>
-    <row r="574" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="574" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A574">
         <v>594</v>
       </c>
       <c r="B574" t="s">
+        <v>1126</v>
+      </c>
+      <c r="C574" t="s">
         <v>1127</v>
       </c>
-      <c r="C574" t="s">
-        <v>1128</v>
-      </c>
-    </row>
-    <row r="575" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="575" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A575">
         <v>595</v>
       </c>
       <c r="B575" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C575" t="s">
         <v>1129</v>
       </c>
-      <c r="C575" t="s">
-        <v>1130</v>
-      </c>
-    </row>
-    <row r="576" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="576" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A576">
         <v>596</v>
       </c>
       <c r="B576" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="577" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A577">
         <v>597</v>
       </c>
       <c r="B577" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="578" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A578">
         <v>598</v>
       </c>
       <c r="B578" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="579" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A579">
         <v>599</v>
       </c>
       <c r="B579" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C579" t="s">
         <v>1132</v>
       </c>
-      <c r="C579" t="s">
-        <v>1133</v>
-      </c>
-    </row>
-    <row r="580" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="580" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A580">
         <v>601</v>
       </c>
       <c r="B580" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C580" t="s">
         <v>1134</v>
       </c>
-      <c r="C580" t="s">
-        <v>1135</v>
-      </c>
-    </row>
-    <row r="581" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="581" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A581">
         <v>604</v>
       </c>
       <c r="B581" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C581" t="s">
         <v>1136</v>
       </c>
-      <c r="C581" t="s">
-        <v>1137</v>
-      </c>
-    </row>
-    <row r="582" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="582" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A582">
         <v>612</v>
       </c>
       <c r="B582" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C582" t="s">
         <v>1138</v>
       </c>
-      <c r="C582" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="583" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="583" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A583">
         <v>617</v>
       </c>
       <c r="B583" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C583" t="s">
         <v>1140</v>
       </c>
-      <c r="C583" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="584" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="584" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A584">
         <v>618</v>
       </c>
       <c r="B584" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C584" t="s">
         <v>1142</v>
       </c>
-      <c r="C584" t="s">
-        <v>1143</v>
-      </c>
-    </row>
-    <row r="585" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="585" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A585">
         <v>626</v>
       </c>
       <c r="B585" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C585" t="s">
         <v>1144</v>
       </c>
-      <c r="C585" t="s">
-        <v>1145</v>
-      </c>
-    </row>
-    <row r="586" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="586" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A586">
         <v>629</v>
       </c>
       <c r="B586" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C586" t="s">
         <v>1146</v>
       </c>
-      <c r="C586" t="s">
-        <v>1147</v>
-      </c>
-    </row>
-    <row r="587" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="587" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A587">
         <v>633</v>
       </c>
       <c r="B587" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C587" t="s">
         <v>1148</v>
       </c>
-      <c r="C587" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="588" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="588" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A588">
         <v>635</v>
       </c>
       <c r="B588" t="s">
+        <v>1149</v>
+      </c>
+      <c r="C588" t="s">
         <v>1150</v>
       </c>
-      <c r="C588" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="589" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="589" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A589">
         <v>636</v>
       </c>
       <c r="B589" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C589" t="s">
         <v>1152</v>
       </c>
-      <c r="C589" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="590" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="590" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A590">
         <v>642</v>
       </c>
       <c r="B590" t="s">
+        <v>1153</v>
+      </c>
+      <c r="C590" t="s">
         <v>1154</v>
       </c>
-      <c r="C590" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="591" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="591" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A591">
         <v>646</v>
       </c>
       <c r="B591" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C591" t="s">
         <v>1156</v>
       </c>
-      <c r="C591" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="592" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="592" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A592">
         <v>650</v>
       </c>
       <c r="B592" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C592" t="s">
         <v>1158</v>
       </c>
-      <c r="C592" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="593" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="593" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A593">
         <v>651</v>
       </c>
       <c r="B593" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C593" t="s">
         <v>1160</v>
       </c>
-      <c r="C593" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="594" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="594" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A594">
         <v>653</v>
       </c>
       <c r="B594" t="s">
+        <v>1161</v>
+      </c>
+      <c r="C594" t="s">
         <v>1162</v>
       </c>
-      <c r="C594" t="s">
-        <v>1163</v>
-      </c>
-    </row>
-    <row r="595" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="595" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A595">
         <v>655</v>
       </c>
       <c r="B595" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C595" t="s">
         <v>1164</v>
       </c>
-      <c r="C595" t="s">
-        <v>1165</v>
-      </c>
-    </row>
-    <row r="596" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="596" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A596">
         <v>661</v>
       </c>
       <c r="B596" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C596" t="s">
         <v>1166</v>
       </c>
-      <c r="C596" t="s">
-        <v>1167</v>
-      </c>
-    </row>
-    <row r="597" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="597" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A597">
         <v>667</v>
       </c>
       <c r="B597" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C597" t="s">
         <v>1168</v>
       </c>
-      <c r="C597" t="s">
-        <v>1169</v>
-      </c>
-    </row>
-    <row r="598" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="598" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A598">
         <v>673</v>
       </c>
       <c r="B598" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C598" t="s">
         <v>1170</v>
       </c>
-      <c r="C598" t="s">
-        <v>1171</v>
-      </c>
-    </row>
-    <row r="599" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="599" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A599">
         <v>674</v>
       </c>
       <c r="B599" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C599" t="s">
         <v>1172</v>
       </c>
-      <c r="C599" t="s">
-        <v>1173</v>
-      </c>
-    </row>
-    <row r="600" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="600" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A600">
         <v>680</v>
       </c>
       <c r="B600" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C600" t="s">
         <v>1174</v>
       </c>
-      <c r="C600" t="s">
-        <v>1175</v>
-      </c>
-    </row>
-    <row r="601" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="601" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A601">
         <v>682</v>
       </c>
       <c r="B601" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C601" t="s">
         <v>1176</v>
       </c>
-      <c r="C601" t="s">
-        <v>1177</v>
-      </c>
-    </row>
-    <row r="602" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="602" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A602">
         <v>685</v>
       </c>
       <c r="B602" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C602" t="s">
         <v>1178</v>
       </c>
-      <c r="C602" t="s">
-        <v>1179</v>
-      </c>
-    </row>
-    <row r="603" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="603" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A603">
         <v>686</v>
       </c>
       <c r="B603" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C603" t="s">
         <v>1180</v>
       </c>
-      <c r="C603" t="s">
-        <v>1181</v>
-      </c>
-    </row>
-    <row r="604" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="604" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A604">
         <v>689</v>
       </c>
       <c r="B604" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C604" t="s">
         <v>1182</v>
       </c>
-      <c r="C604" t="s">
-        <v>1183</v>
-      </c>
-    </row>
-    <row r="605" spans="1:3" ht="15.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="605" spans="1:3" hidden="1" x14ac:dyDescent="0.25">
       <c r="A605">
         <v>10001</v>
       </c>
       <c r="B605" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C605" t="s">
         <v>1184</v>
       </c>
-      <c r="C605" t="s">
-        <v>1185</v>
-      </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:C605" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Believe in my existence"/>
+        <filter val="EXIST"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:C119 A121:C605 A120:B120" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:C119 A121:C314 A120:B120 A316:C605 A315:B315" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>